--- a/отчеты для СН/НЕДОГРУЗЫ ПОКОМ/08,26/15,08,26/Луганск.xlsx
+++ b/отчеты для СН/НЕДОГРУЗЫ ПОКОМ/08,26/15,08,26/Луганск.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\отчеты для СН\НЕДОГРУЗЫ ПОКОМ\08,26\15,08,26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABB7E32-8E9C-4FE0-8912-0C993973B2CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F67A62-0FD5-4562-A0D3-2A18321FF6EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,25 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$K$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$M$77</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="505">
   <si>
     <t>Код единицы продаж</t>
   </si>
@@ -1318,6 +1324,231 @@
   </si>
   <si>
     <t> 1 522 534.03</t>
+  </si>
+  <si>
+    <t>SU000227</t>
+  </si>
+  <si>
+    <t>SU001051</t>
+  </si>
+  <si>
+    <t>SU001430</t>
+  </si>
+  <si>
+    <t>SU001523</t>
+  </si>
+  <si>
+    <t>SU001718</t>
+  </si>
+  <si>
+    <t>SU001720</t>
+  </si>
+  <si>
+    <t>SU001822</t>
+  </si>
+  <si>
+    <t>SU002011</t>
+  </si>
+  <si>
+    <t>SU002035</t>
+  </si>
+  <si>
+    <t>SU002074</t>
+  </si>
+  <si>
+    <t>SU002092</t>
+  </si>
+  <si>
+    <t>SU002150</t>
+  </si>
+  <si>
+    <t>SU002151</t>
+  </si>
+  <si>
+    <t>SU002158</t>
+  </si>
+  <si>
+    <t>SU002182</t>
+  </si>
+  <si>
+    <t>SU002287</t>
+  </si>
+  <si>
+    <t>SU002618</t>
+  </si>
+  <si>
+    <t>SU002621</t>
+  </si>
+  <si>
+    <t>SU002632</t>
+  </si>
+  <si>
+    <t>SU002643</t>
+  </si>
+  <si>
+    <t>SU002655</t>
+  </si>
+  <si>
+    <t>SU002660</t>
+  </si>
+  <si>
+    <t>SU002686</t>
+  </si>
+  <si>
+    <t>SU002725</t>
+  </si>
+  <si>
+    <t>SU002734</t>
+  </si>
+  <si>
+    <t>SU002735</t>
+  </si>
+  <si>
+    <t>SU002756</t>
+  </si>
+  <si>
+    <t>SU002759</t>
+  </si>
+  <si>
+    <t>SU002799</t>
+  </si>
+  <si>
+    <t>SU002801</t>
+  </si>
+  <si>
+    <t>SU002815</t>
+  </si>
+  <si>
+    <t>SU002816</t>
+  </si>
+  <si>
+    <t>SU002830</t>
+  </si>
+  <si>
+    <t>SU002831</t>
+  </si>
+  <si>
+    <t>SU002833</t>
+  </si>
+  <si>
+    <t>SU002840</t>
+  </si>
+  <si>
+    <t>SU002841</t>
+  </si>
+  <si>
+    <t>SU002842</t>
+  </si>
+  <si>
+    <t>SU002843</t>
+  </si>
+  <si>
+    <t>SU002844</t>
+  </si>
+  <si>
+    <t>SU002845</t>
+  </si>
+  <si>
+    <t>SU002918</t>
+  </si>
+  <si>
+    <t>SU002928</t>
+  </si>
+  <si>
+    <t>SU002941</t>
+  </si>
+  <si>
+    <t>SU002942</t>
+  </si>
+  <si>
+    <t>SU002943</t>
+  </si>
+  <si>
+    <t>SU002944</t>
+  </si>
+  <si>
+    <t>SU002945</t>
+  </si>
+  <si>
+    <t>SU002947</t>
+  </si>
+  <si>
+    <t>SU002948</t>
+  </si>
+  <si>
+    <t>SU002983</t>
+  </si>
+  <si>
+    <t>SU002984</t>
+  </si>
+  <si>
+    <t>SU002985</t>
+  </si>
+  <si>
+    <t>SU002986</t>
+  </si>
+  <si>
+    <t>SU003167</t>
+  </si>
+  <si>
+    <t>SU003168</t>
+  </si>
+  <si>
+    <t>SU003273</t>
+  </si>
+  <si>
+    <t>SU003392</t>
+  </si>
+  <si>
+    <t>SU003642</t>
+  </si>
+  <si>
+    <t>SU003829</t>
+  </si>
+  <si>
+    <t>SU003896</t>
+  </si>
+  <si>
+    <t>SU003921</t>
+  </si>
+  <si>
+    <t>SU004016</t>
+  </si>
+  <si>
+    <t>SU004026</t>
+  </si>
+  <si>
+    <t>SU004041</t>
+  </si>
+  <si>
+    <t>SU004042</t>
+  </si>
+  <si>
+    <t>SU004044</t>
+  </si>
+  <si>
+    <t>SU004047</t>
+  </si>
+  <si>
+    <t>SU004103</t>
+  </si>
+  <si>
+    <t>SU004104</t>
+  </si>
+  <si>
+    <t>SU004106</t>
+  </si>
+  <si>
+    <t>SU004131</t>
+  </si>
+  <si>
+    <t>SU004144</t>
+  </si>
+  <si>
+    <t>SU004146</t>
+  </si>
+  <si>
+    <t>SU004157</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1593,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1411,11 +1642,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1430,6 +1672,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1712,2741 +1957,3242 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="76.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="1" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="76.5703125" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2" t="str">
+        <f>MID(A2,2,8)</f>
+        <v>SU000227</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="2" t="str">
+        <f t="shared" ref="B3:B66" si="0">MID(A3,2,8)</f>
+        <v>SU001051</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU001430</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU001523</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU001718</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU001720</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU001822</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002011</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002035</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002074</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002092</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002150</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002151</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002158</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>96</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002182</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="L16" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002287</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002618</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002621</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002632</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002643</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>127</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002655</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002660</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002686</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>144</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>23</v>
+        <v>144</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="M24" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002725</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="M25" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002734</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>157</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="L26" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="M26" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002735</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>163</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002756</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="M28" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002759</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>174</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>23</v>
+        <v>174</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002799</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="L30" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="M30" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002801</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>185</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="G31" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="K31" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="L31" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="M31" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002815</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>127</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="G32" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="M32" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002816</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>138</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="G33" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="K33" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="L33" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="M33" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002830</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="F34" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="G34" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="I34" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="K34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="M34" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002831</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>205</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>23</v>
+        <v>205</v>
       </c>
       <c r="G35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="K35" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="L35" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="M35" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002833</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="G36" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="H36" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="I36" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="J36" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="K36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="L36" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="M36" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002840</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>175</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="G37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="K37" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002841</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>152</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="G38" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="K38" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="L38" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="M38" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002842</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>101</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="G39" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="J39" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="K39" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="L39" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="M39" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002843</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="F40" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="I40" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="3" t="s">
+      <c r="J40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="L40" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="M40" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002844</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>211</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>23</v>
+        <v>211</v>
       </c>
       <c r="G41" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="J41" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="K41" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="L41" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="M41" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002845</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="H42" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="J42" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="K42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="L42" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="M42" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002918</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="G43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="L43" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="M43" s="3" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002928</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="G44" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="K44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="L44" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="M44" s="3" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002941</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="I45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="M45" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002942</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="I46" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" s="3" t="s">
+      <c r="J46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="M46" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002943</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002944</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="I48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I48" s="3" t="s">
+      <c r="J48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="L48" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="M48" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002945</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I49" s="3" t="s">
+      <c r="J49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="L49" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="M49" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002947</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>133</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="G50" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="J50" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="K50" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="L50" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="K50" s="3" t="s">
+      <c r="M50" s="3" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002948</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="I51" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I51" s="3" t="s">
+      <c r="J51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K51" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="L51" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="K51" s="3" t="s">
+      <c r="M51" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002983</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>289</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>23</v>
+        <v>289</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="M52" s="3" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002984</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>294</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>23</v>
+        <v>294</v>
       </c>
       <c r="G53" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="J53" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="K53" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="L53" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="K53" s="3" t="s">
+      <c r="M53" s="3" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002985</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>301</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>23</v>
+        <v>301</v>
       </c>
       <c r="G54" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="J54" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="K54" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="L54" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="K54" s="3" t="s">
+      <c r="M54" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU002986</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>307</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>23</v>
+        <v>307</v>
       </c>
       <c r="G55" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="J55" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="I55" s="3" t="s">
+      <c r="K55" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="L55" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="K55" s="3" t="s">
+      <c r="M55" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU003167</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>138</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="G56" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="J56" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="L56" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="M56" s="3" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU003168</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>318</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>23</v>
+        <v>318</v>
       </c>
       <c r="G57" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="J57" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="K57" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="L57" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="K57" s="3" t="s">
+      <c r="M57" s="3" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU003273</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>324</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>23</v>
+        <v>324</v>
       </c>
       <c r="G58" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="J58" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="K58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="L58" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="M58" s="3" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU003392</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>96</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="G59" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="J59" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="K59" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="L59" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="M59" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU003642</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="F60" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="G60" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="H60" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="I60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="J60" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I60" s="3" t="s">
+      <c r="K60" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="L60" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="K60" s="3" t="s">
+      <c r="M60" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU003829</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>338</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>23</v>
+        <v>338</v>
       </c>
       <c r="G61" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="J61" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="I61" s="3" t="s">
+      <c r="K61" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="L61" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="K61" s="3" t="s">
+      <c r="M61" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU003896</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="J62" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="K62" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="L62" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="M62" s="3" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU003921</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>96</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="G63" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="J63" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="I63" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="L63" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="K63" s="3" t="s">
+      <c r="M63" s="3" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU004016</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="J64" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="K64" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="J64" s="3" t="s">
+      <c r="L64" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="K64" s="3" t="s">
+      <c r="M64" s="3" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU004026</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>152</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="G65" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="J65" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="K65" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="L65" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="M65" s="3" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SU004041</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>366</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>23</v>
+        <v>366</v>
       </c>
       <c r="G66" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="J66" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="K66" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="L66" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="M66" s="3" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="2" t="str">
+        <f t="shared" ref="B67:B76" si="1">MID(A67,2,8)</f>
+        <v>SU004042</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="J67" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="K67" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="L67" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="K67" s="3" t="s">
+      <c r="M67" s="3" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SU004044</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="I68" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I68" s="3" t="s">
+      <c r="J68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="L68" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="K68" s="3" t="s">
+      <c r="M68" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SU004047</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="I69" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H69" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I69" s="3" t="s">
+      <c r="J69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="L69" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="K69" s="3" t="s">
+      <c r="M69" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SU004103</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="G70" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="H70" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="I70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="J70" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="K70" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="L70" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="K70" s="3" t="s">
+      <c r="M70" s="3" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SU004104</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="F71" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="G71" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="H71" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="I71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="J71" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="I71" s="3" t="s">
+      <c r="K71" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="L71" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="M71" s="3" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SU004106</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="G72" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="J72" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="K72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J72" s="3" t="s">
+      <c r="L72" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="K72" s="3" t="s">
+      <c r="M72" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SU004131</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="F73" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="G73" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="H73" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="I73" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="J73" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I73" s="3" t="s">
+      <c r="K73" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="L73" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="K73" s="3" t="s">
+      <c r="M73" s="3" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SU004144</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G74" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H74" s="3" t="s">
+      <c r="J74" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="K74" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="L74" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K74" s="3" t="s">
+      <c r="M74" s="3" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SU004146</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>23</v>
+        <v>412</v>
       </c>
       <c r="G75" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H75" s="3" t="s">
+      <c r="J75" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="K75" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="J75" s="3" t="s">
+      <c r="L75" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="K75" s="3" t="s">
+      <c r="M75" s="3" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SU004157</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="F76" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="G76" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="H76" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="I76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="J76" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="K76" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="L76" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="K76" s="3" t="s">
+      <c r="M76" s="3" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="B77" s="5"/>
-      <c r="C77" s="3" t="s">
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="F77" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="G77" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="H77" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>428</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>427</v>
       </c>
       <c r="J77" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="K77" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="K77" s="3" t="s">
+      <c r="L77" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="M77" s="3" t="s">
         <v>429</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K77" xr:uid="{5E0A23E5-2909-44B9-9B45-91689F5DE8D7}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val=" -1 008 "/>
-        <filter val=" -1 "/>
-        <filter val=" -105 "/>
-        <filter val=" -108 "/>
-        <filter val=" -119 "/>
-        <filter val=" -169 "/>
-        <filter val=" -178 "/>
-        <filter val=" -192 "/>
-        <filter val=" -29 "/>
-        <filter val=" -3 247 "/>
-        <filter val=" -3 "/>
-        <filter val=" -36 "/>
-        <filter val=" -45 "/>
-        <filter val=" -50 "/>
-        <filter val=" -54 "/>
-        <filter val=" -6 "/>
-        <filter val=" -60 "/>
-        <filter val=" -63 "/>
-        <filter val=" -73 "/>
-        <filter val=" -768 "/>
-        <filter val=" -80 "/>
-        <filter val=" -91 "/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M77" xr:uid="{5E0A23E5-2909-44B9-9B45-91689F5DE8D7}"/>
   <mergeCells count="1">
-    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A77:D77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
